--- a/employee_evaluation_forms/010_employee_payroll_change_form--employee_evaluation_forms.xlsx
+++ b/employee_evaluation_forms/010_employee_payroll_change_form--employee_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1033,8 +1033,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'option_1'}</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'option_2'}</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'option_3'}</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'option_1'}</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'option_2'}</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'option_3'}</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'option_4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'option_4'}</t>
+          <t>option 4</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_25,_'name':_'option_5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 25, 'name': 'option_5'}</t>
+          <t>option 5</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_27,_'name':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 27, 'name': 'option_1'}</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_28,_'name':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 28, 'name': 'option_2'}</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_29,_'name':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 29, 'name': 'option_3'}</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_31,_'name':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 31, 'name': 'option_1'}</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_32,_'name':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 32, 'name': 'option_2'}</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_33,_'name':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 33, 'name': 'option_3'}</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
